--- a/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
+++ b/KURIKULUM2026_REVISI/024_MATRIKS_EKIVALENSI_KURIKULUM2025_KE_KURIKULUM2026.xlsx
@@ -4003,7 +4003,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-626` Deep Learning &amp; `STA-703` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
+          <t>**Dihapus** dari K2026 (bertumpang dengan ranah riset algoritma Prodi TI, Dok. 016). Unsur ekstraksi fitur sinyal terserap parsial pada `STI-726` Deep Learning &amp; `STA-703` Smart Surveillance. Diakui sebagai kredit bebas 3 SKS</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
@@ -6667,7 +6667,7 @@
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -6699,7 +6699,7 @@
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="207" ht="16" customHeight="1">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -7000,7 +7000,7 @@
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>**Migrasi selektif.** `STI-103` dan `STI-312` wajib pada Sem 5 karena menjadi prasyarat Cloud, IoT, dan Keamanan; `FST-610` Capstone pada Sem 7</t>
+          <t>**Migrasi selektif.** `STI-103` dan `STI-312` wajib pada Sem 5 karena menjadi prasyarat Cloud, IoT, dan Keamanan; `FST-610` Capstone pada Sem 6</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>**Tetap pada K2025** dengan penyisipan `FST-610` Capstone Project FSTI sebagai pengganti 3 SKS MK pilihan. Migrasi penuh tidak efisien karena defisit melampaui 24 SKS</t>
+          <t>**Tetap pada K2025** dengan penyisipan `FST-610` Capstone Project FSTI sebagai pengganti 3 SKS MK pilihan di Sem 6. Migrasi penuh tidak efisien karena defisit melampaui 24 SKS</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="D364" s="8" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="D366" s="8" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="D368" s="8" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="C369" s="9" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="D369" s="10" t="inlineStr">
